--- a/file/table2.xlsx
+++ b/file/table2.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,8 +131,8 @@
   </si>
   <si>
     <t>设防水位：8.5
-警戒水位：9.5
-保证水位：11.5</t>
+警戒水位：10.5
+保证水位：12.65</t>
   </si>
   <si>
     <r>
@@ -1377,23 +1377,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="3.75454545454545" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.8181818181818" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.6272727272727" style="2" customWidth="1"/>
-    <col min="4" max="6" width="11.8727272727273" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.2545454545455" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.75833333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.8166666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="4" max="6" width="11.875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.2583333333333" style="2" customWidth="1"/>
     <col min="9" max="16382" width="9" style="2" customWidth="1"/>
     <col min="16383" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:1">
+    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:1">
+    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1563,7 +1563,7 @@
       <c r="B11" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="14"/>
@@ -1648,7 +1648,7 @@
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:1">
+    <row r="16" s="2" customFormat="1" spans="1:8">
       <c r="A16" s="27" t="s">
         <v>28</v>
       </c>
